--- a/src/Excelsior.Tests/StyleTests.GlobalStyle.verified.xlsx
+++ b/src/Excelsior.Tests/StyleTests.GlobalStyle.verified.xlsx
@@ -263,22 +263,22 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="A2:A5">
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." prompt="This field is required." sqref="A2:A5">
       <formula1>ISNUMBER(A2)</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="B2:B5">
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="This field is required." sqref="B2:B5">
       <formula1>LEN(TRIM(B2))&gt;0</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="C2:C5">
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="This field is required." sqref="C2:C5">
       <formula1>LEN(TRIM(C2))&gt;0</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="E2:E5">
       <formula1>ISNUMBER(E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." sqref="F2:F5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." prompt="Select one of: TRUE, FALSE." sqref="F2:F5">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Full Time, Part Time, Contract, Terminated." sqref="G2:G5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Full Time, Part Time, Contract, Terminated." prompt="Select one of: Full Time, Part Time, Contract, Terminated." sqref="G2:G5">
       <formula1>"Full Time,Part Time,Contract,Terminated"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/StyleTests.GlobalStyle.verified.xlsx
+++ b/src/Excelsior.Tests/StyleTests.GlobalStyle.verified.xlsx
@@ -263,22 +263,22 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." prompt="This field is required." sqref="A2:A5">
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." prompt="Required field" sqref="A2:A5">
       <formula1>ISNUMBER(A2)</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="This field is required." sqref="B2:B5">
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="Required field" sqref="B2:B5">
       <formula1>LEN(TRIM(B2))&gt;0</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="This field is required." sqref="C2:C5">
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="Required field" sqref="C2:C5">
       <formula1>LEN(TRIM(C2))&gt;0</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="E2:E5">
       <formula1>ISNUMBER(E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." prompt="Select one of: TRUE, FALSE." sqref="F2:F5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." prompt="Select one of: TRUE, FALSE" sqref="F2:F5">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Full Time, Part Time, Contract, Terminated." prompt="Select one of: Full Time, Part Time, Contract, Terminated." sqref="G2:G5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Full Time, Part Time, Contract, Terminated." prompt="Select one of: Full Time, Part Time, Contract, Terminated" sqref="G2:G5">
       <formula1>"Full Time,Part Time,Contract,Terminated"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/StyleTests.GlobalStyle.verified.xlsx
+++ b/src/Excelsior.Tests/StyleTests.GlobalStyle.verified.xlsx
@@ -263,22 +263,22 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="A2:A5">
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." prompt="Required field" sqref="A2:A5">
       <formula1>ISNUMBER(A2)</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="B2:B5">
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="Required field" sqref="B2:B5">
       <formula1>LEN(TRIM(B2))&gt;0</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="C2:C5">
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="Required field" sqref="C2:C5">
       <formula1>LEN(TRIM(C2))&gt;0</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="E2:E5">
       <formula1>ISNUMBER(E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." sqref="F2:F5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." prompt="Select one of: TRUE, FALSE" sqref="F2:F5">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Full Time, Part Time, Contract, Terminated." sqref="G2:G5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Full Time, Part Time, Contract, Terminated." prompt="Select one of: Full Time, Part Time, Contract, Terminated" sqref="G2:G5">
       <formula1>"Full Time,Part Time,Contract,Terminated"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/StyleTests.GlobalStyle.verified.xlsx
+++ b/src/Excelsior.Tests/StyleTests.GlobalStyle.verified.xlsx
@@ -25,8 +25,8 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <color rgb="FFFFFF"/>
     </font>
   </fonts>
   <fills count="3">
@@ -38,7 +38,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00008B"/>
+        <fgColor rgb="FF00008B"/>
       </patternFill>
     </fill>
   </fills>

--- a/src/Excelsior.Tests/StyleTests.GlobalStyle.verified.xlsx
+++ b/src/Excelsior.Tests/StyleTests.GlobalStyle.verified.xlsx
@@ -286,7 +286,7 @@
 </file>
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
-<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+<columnMetadata xmlns="https://github.com/Papyrine/Excelsior/columnMetadata/v1">
   <sheet name="Sheet1">
     <column index="1" property="Id"/>
     <column index="2" property="Name"/>
